--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/92.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/92.xlsx
@@ -426,13 +426,13 @@
         <v>-10.53283485746315</v>
       </c>
       <c r="E2">
-        <v>-13.21236388249278</v>
+        <v>-12.8521781168707</v>
       </c>
       <c r="F2">
-        <v>-4.772169254159472</v>
+        <v>-4.36467296280252</v>
       </c>
       <c r="G2">
-        <v>-10.12509280761475</v>
+        <v>-10.50895387343878</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.75540076840857</v>
       </c>
       <c r="E3">
-        <v>-14.69704219980354</v>
+        <v>-13.08441184940606</v>
       </c>
       <c r="F3">
-        <v>-4.590186876173254</v>
+        <v>-4.581460025584762</v>
       </c>
       <c r="G3">
-        <v>-10.12092152023526</v>
+        <v>-10.48950441839556</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.898337181915689</v>
       </c>
       <c r="E4">
-        <v>-13.39792263343108</v>
+        <v>-14.18932780795957</v>
       </c>
       <c r="F4">
-        <v>-4.29398588721943</v>
+        <v>-4.505714110272774</v>
       </c>
       <c r="G4">
-        <v>-9.781415143546386</v>
+        <v>-9.813269212725254</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.05851476952488</v>
       </c>
       <c r="E5">
-        <v>-13.77018583923162</v>
+        <v>-14.70549233230185</v>
       </c>
       <c r="F5">
-        <v>-4.010970850583367</v>
+        <v>-4.115332717825063</v>
       </c>
       <c r="G5">
-        <v>-9.668777142118223</v>
+        <v>-8.789853785806038</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.232054108043812</v>
       </c>
       <c r="E6">
-        <v>-15.57393137817482</v>
+        <v>-15.03647849752248</v>
       </c>
       <c r="F6">
-        <v>-4.486824848386737</v>
+        <v>-4.803768157106662</v>
       </c>
       <c r="G6">
-        <v>-9.373032866912972</v>
+        <v>-9.172837557062165</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.440327471535118</v>
       </c>
       <c r="E7">
-        <v>-15.67008899525369</v>
+        <v>-16.50700986203328</v>
       </c>
       <c r="F7">
-        <v>-4.245803897235596</v>
+        <v>-4.581071521272849</v>
       </c>
       <c r="G7">
-        <v>-8.183093688822876</v>
+        <v>-8.912036090023919</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.692468085443815</v>
       </c>
       <c r="E8">
-        <v>-17.04570354456372</v>
+        <v>-17.14069734382262</v>
       </c>
       <c r="F8">
-        <v>-4.04248774515768</v>
+        <v>-4.461307818910901</v>
       </c>
       <c r="G8">
-        <v>-8.033122665348351</v>
+        <v>-8.685353105313403</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.994985568763803</v>
       </c>
       <c r="E9">
-        <v>-17.60076313215788</v>
+        <v>-17.55326396829143</v>
       </c>
       <c r="F9">
-        <v>-4.635035515728222</v>
+        <v>-4.374113866092226</v>
       </c>
       <c r="G9">
-        <v>-7.863576386100116</v>
+        <v>-7.816553397260309</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.342110600857177</v>
       </c>
       <c r="E10">
-        <v>-18.27186033772459</v>
+        <v>-18.15616235530262</v>
       </c>
       <c r="F10">
-        <v>-4.397400930519725</v>
+        <v>-4.681147415572459</v>
       </c>
       <c r="G10">
-        <v>-7.413941401501843</v>
+        <v>-7.527211717128007</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.745131137677511</v>
       </c>
       <c r="E11">
-        <v>-17.83057413109914</v>
+        <v>-18.92868832169313</v>
       </c>
       <c r="F11">
-        <v>-4.234200955024583</v>
+        <v>-4.621590284413384</v>
       </c>
       <c r="G11">
-        <v>-7.185748808025419</v>
+        <v>-6.808028804176734</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.203165871015313</v>
       </c>
       <c r="E12">
-        <v>-19.38207461086708</v>
+        <v>-19.38082022356695</v>
       </c>
       <c r="F12">
-        <v>-4.126889271461518</v>
+        <v>-4.365786288591882</v>
       </c>
       <c r="G12">
-        <v>-6.74654535242139</v>
+        <v>-6.606297401195705</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.715078554442819</v>
       </c>
       <c r="E13">
-        <v>-19.5547136254615</v>
+        <v>-19.41423130479554</v>
       </c>
       <c r="F13">
-        <v>-3.599865362452417</v>
+        <v>-4.229781614930648</v>
       </c>
       <c r="G13">
-        <v>-6.852803932595377</v>
+        <v>-6.522375071775181</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.294223568471313</v>
       </c>
       <c r="E14">
-        <v>-22.19318824976456</v>
+        <v>-20.92814997877383</v>
       </c>
       <c r="F14">
-        <v>-4.263470488835101</v>
+        <v>-4.107879067934673</v>
       </c>
       <c r="G14">
-        <v>-6.889478156079423</v>
+        <v>-5.454988979003365</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.943477065530718</v>
       </c>
       <c r="E15">
-        <v>-22.26481059466987</v>
+        <v>-22.56419253979097</v>
       </c>
       <c r="F15">
-        <v>-3.732458819148923</v>
+        <v>-4.244486793065145</v>
       </c>
       <c r="G15">
-        <v>-5.499224488499106</v>
+        <v>-5.198901728813041</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.661567227755403</v>
       </c>
       <c r="E16">
-        <v>-22.39518988982471</v>
+        <v>-22.81634250101206</v>
       </c>
       <c r="F16">
-        <v>-3.74274631392429</v>
+        <v>-3.921675329663789</v>
       </c>
       <c r="G16">
-        <v>-5.271329844121217</v>
+        <v>-5.470657791040735</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.453781540421013</v>
       </c>
       <c r="E17">
-        <v>-23.44638908969924</v>
+        <v>-23.47041264430993</v>
       </c>
       <c r="F17">
-        <v>-3.824738947820788</v>
+        <v>-3.604229201930365</v>
       </c>
       <c r="G17">
-        <v>-4.555646177804953</v>
+        <v>-4.961684588196565</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.312573651672182</v>
       </c>
       <c r="E18">
-        <v>-24.18563530060738</v>
+        <v>-24.47296244792005</v>
       </c>
       <c r="F18">
-        <v>-2.777405047602275</v>
+        <v>-3.350699074629548</v>
       </c>
       <c r="G18">
-        <v>-4.385947613461912</v>
+        <v>-5.072607727035385</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.223956542324056</v>
       </c>
       <c r="E19">
-        <v>-23.97462199727196</v>
+        <v>-25.71025023019178</v>
       </c>
       <c r="F19">
-        <v>-2.955993604339223</v>
+        <v>-2.99812851228262</v>
       </c>
       <c r="G19">
-        <v>-4.452181698066111</v>
+        <v>-4.592519034021356</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.177516632705252</v>
       </c>
       <c r="E20">
-        <v>-25.81430550594003</v>
+        <v>-25.4199705178261</v>
       </c>
       <c r="F20">
-        <v>-2.320253929019312</v>
+        <v>-2.587461230507751</v>
       </c>
       <c r="G20">
-        <v>-5.085869772465705</v>
+        <v>-4.793661159896395</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.156401877071878</v>
       </c>
       <c r="E21">
-        <v>-26.27642722147477</v>
+        <v>-26.22805859059885</v>
       </c>
       <c r="F21">
-        <v>-2.548276138885723</v>
+        <v>-2.350441293912132</v>
       </c>
       <c r="G21">
-        <v>-4.894758599574659</v>
+        <v>-4.705603959097321</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.144567756918229</v>
       </c>
       <c r="E22">
-        <v>-26.27742801423047</v>
+        <v>-27.09419717167592</v>
       </c>
       <c r="F22">
-        <v>-2.456850057006144</v>
+        <v>-2.351968803402894</v>
       </c>
       <c r="G22">
-        <v>-4.25445936573314</v>
+        <v>-5.076974336601684</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.133430380012832</v>
       </c>
       <c r="E23">
-        <v>-27.87694843237575</v>
+        <v>-26.92595983381696</v>
       </c>
       <c r="F23">
-        <v>-1.35562671539851</v>
+        <v>-2.059885628808385</v>
       </c>
       <c r="G23">
-        <v>-4.540556711236956</v>
+        <v>-5.193280422487359</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.115687311338738</v>
       </c>
       <c r="E24">
-        <v>-27.9541453287845</v>
+        <v>-27.74858883662833</v>
       </c>
       <c r="F24">
-        <v>-1.845890992540981</v>
+        <v>-1.921505197435922</v>
       </c>
       <c r="G24">
-        <v>-4.593343359860635</v>
+        <v>-4.327158945775535</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.087733661904327</v>
       </c>
       <c r="E25">
-        <v>-27.35054049982811</v>
+        <v>-28.22897841631002</v>
       </c>
       <c r="F25">
-        <v>-1.559931938155369</v>
+        <v>-1.980276207929742</v>
       </c>
       <c r="G25">
-        <v>-4.559380473173252</v>
+        <v>-4.479066638390533</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.051068468555047</v>
       </c>
       <c r="E26">
-        <v>-28.08299852819876</v>
+        <v>-28.2502803580421</v>
       </c>
       <c r="F26">
-        <v>-1.583437691577207</v>
+        <v>-1.6192687235853</v>
       </c>
       <c r="G26">
-        <v>-4.600557038590707</v>
+        <v>-5.217026965640551</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.007311851663261</v>
       </c>
       <c r="E27">
-        <v>-28.07888214532579</v>
+        <v>-28.2922547836192</v>
       </c>
       <c r="F27">
-        <v>-1.576887790523272</v>
+        <v>-1.600956833779014</v>
       </c>
       <c r="G27">
-        <v>-3.576479502563636</v>
+        <v>-5.364283341772873</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.9589252168489175</v>
       </c>
       <c r="E28">
-        <v>-28.34607116872635</v>
+        <v>-27.81220031101408</v>
       </c>
       <c r="F28">
-        <v>-1.578624876966942</v>
+        <v>-1.262712885663503</v>
       </c>
       <c r="G28">
-        <v>-5.544181696922409</v>
+        <v>-5.106395154809187</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.9094794687656418</v>
       </c>
       <c r="E29">
-        <v>-27.2854119866498</v>
+        <v>-28.52150878025751</v>
       </c>
       <c r="F29">
-        <v>-1.448551313909753</v>
+        <v>-1.477040525626834</v>
       </c>
       <c r="G29">
-        <v>-4.868198092713086</v>
+        <v>-5.508103371635431</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8609423558068705</v>
       </c>
       <c r="E30">
-        <v>-26.41956322790922</v>
+        <v>-27.48605508450765</v>
       </c>
       <c r="F30">
-        <v>-1.733313377398319</v>
+        <v>-1.543768005024542</v>
       </c>
       <c r="G30">
-        <v>-4.045775817119641</v>
+        <v>-4.928281183705319</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8146071727491625</v>
       </c>
       <c r="E31">
-        <v>-27.50697210594908</v>
+        <v>-27.89948211903792</v>
       </c>
       <c r="F31">
-        <v>-2.024567356222625</v>
+        <v>-1.722378927681366</v>
       </c>
       <c r="G31">
-        <v>-4.27040295305027</v>
+        <v>-5.297496396063616</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7714144772107189</v>
       </c>
       <c r="E32">
-        <v>-26.8489395478945</v>
+        <v>-27.55486071858019</v>
       </c>
       <c r="F32">
-        <v>-1.701891745075328</v>
+        <v>-1.466062172437532</v>
       </c>
       <c r="G32">
-        <v>-4.413243061433204</v>
+        <v>-5.312665315724557</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7307740395297053</v>
       </c>
       <c r="E33">
-        <v>-27.1583611198906</v>
+        <v>-27.26177788080377</v>
       </c>
       <c r="F33">
-        <v>-1.568937948558605</v>
+        <v>-1.390823217976058</v>
       </c>
       <c r="G33">
-        <v>-5.203622566752043</v>
+        <v>-5.429487846714358</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6907692495566135</v>
       </c>
       <c r="E34">
-        <v>-25.05598536251158</v>
+        <v>-26.32847750171894</v>
       </c>
       <c r="F34">
-        <v>-1.794653983575623</v>
+        <v>-1.95223928481459</v>
       </c>
       <c r="G34">
-        <v>-5.136799205041854</v>
+        <v>-5.301972253632711</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.6501754388413903</v>
       </c>
       <c r="E35">
-        <v>-24.79963297741137</v>
+        <v>-25.82722524228391</v>
       </c>
       <c r="F35">
-        <v>-1.914734122285439</v>
+        <v>-1.864771142385587</v>
       </c>
       <c r="G35">
-        <v>-4.042895642500475</v>
+        <v>-5.645318863147144</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6079275286953517</v>
       </c>
       <c r="E36">
-        <v>-24.5255923728372</v>
+        <v>-25.6758428846815</v>
       </c>
       <c r="F36">
-        <v>-1.791718249500101</v>
+        <v>-1.818018086171583</v>
       </c>
       <c r="G36">
-        <v>-5.279463854511206</v>
+        <v>-5.884353493264681</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5630199907833119</v>
       </c>
       <c r="E37">
-        <v>-26.34850694225486</v>
+        <v>-25.3243834884722</v>
       </c>
       <c r="F37">
-        <v>-2.048521256409379</v>
+        <v>-2.006842778904924</v>
       </c>
       <c r="G37">
-        <v>-4.681526361390201</v>
+        <v>-5.489051182056926</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5158181985182758</v>
       </c>
       <c r="E38">
-        <v>-24.21481678711281</v>
+        <v>-24.1264300314311</v>
       </c>
       <c r="F38">
-        <v>-1.977735605105355</v>
+        <v>-1.902625875958719</v>
       </c>
       <c r="G38">
-        <v>-4.400272344010339</v>
+        <v>-5.451142125086731</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4666608519021208</v>
       </c>
       <c r="E39">
-        <v>-23.64306524432637</v>
+        <v>-23.94300419175041</v>
       </c>
       <c r="F39">
-        <v>-2.004815763870274</v>
+        <v>-2.203930436481191</v>
       </c>
       <c r="G39">
-        <v>-4.737646729371926</v>
+        <v>-5.78955602174765</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4165025057427887</v>
       </c>
       <c r="E40">
-        <v>-22.58631866379245</v>
+        <v>-23.80979007186677</v>
       </c>
       <c r="F40">
-        <v>-2.308021427582172</v>
+        <v>-2.189476253669743</v>
       </c>
       <c r="G40">
-        <v>-3.445342172662026</v>
+        <v>-5.077057100240165</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3678956585444493</v>
       </c>
       <c r="E41">
-        <v>-22.68775195309025</v>
+        <v>-22.67552054479554</v>
       </c>
       <c r="F41">
-        <v>-2.001443480173477</v>
+        <v>-2.152167414215056</v>
       </c>
       <c r="G41">
-        <v>-4.861937851098324</v>
+        <v>-5.204506482411028</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.323456306861624</v>
       </c>
       <c r="E42">
-        <v>-21.77170053150064</v>
+        <v>-21.18265927495292</v>
       </c>
       <c r="F42">
-        <v>-2.296826042133336</v>
+        <v>-2.446301626498896</v>
       </c>
       <c r="G42">
-        <v>-4.8714953960702</v>
+        <v>-5.368103711325192</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.2877272843236265</v>
       </c>
       <c r="E43">
-        <v>-21.55108686326896</v>
+        <v>-21.19739040089987</v>
       </c>
       <c r="F43">
-        <v>-1.972874745185728</v>
+        <v>-2.490898442363413</v>
       </c>
       <c r="G43">
-        <v>-5.327489938649413</v>
+        <v>-4.917707301252887</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.2667345744298599</v>
       </c>
       <c r="E44">
-        <v>-20.93324451203246</v>
+        <v>-20.72675515423071</v>
       </c>
       <c r="F44">
-        <v>-2.392995355761345</v>
+        <v>-2.431186406500013</v>
       </c>
       <c r="G44">
-        <v>-6.710013482395532</v>
+        <v>-4.998031067672223</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.2657063849840941</v>
       </c>
       <c r="E45">
-        <v>-20.60471277972399</v>
+        <v>-19.85693039531139</v>
       </c>
       <c r="F45">
-        <v>-2.255870729371526</v>
+        <v>-2.389727446357301</v>
       </c>
       <c r="G45">
-        <v>-5.67249513147902</v>
+        <v>-5.554729095010527</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.2917358310516009</v>
       </c>
       <c r="E46">
-        <v>-20.99121350780465</v>
+        <v>-19.02792982957122</v>
       </c>
       <c r="F46">
-        <v>-2.445842710957745</v>
+        <v>-2.597708135280381</v>
       </c>
       <c r="G46">
-        <v>-6.702184042195156</v>
+        <v>-4.884413144764436</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.351300736550815</v>
       </c>
       <c r="E47">
-        <v>-19.24361198960855</v>
+        <v>-19.51175652102473</v>
       </c>
       <c r="F47">
-        <v>-1.838564911230622</v>
+        <v>-2.686765914755356</v>
       </c>
       <c r="G47">
-        <v>-5.804860673775701</v>
+        <v>-5.52051129631662</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4467882001096201</v>
       </c>
       <c r="E48">
-        <v>-17.8159698024244</v>
+        <v>-18.05366487461301</v>
       </c>
       <c r="F48">
-        <v>-2.302667689057878</v>
+        <v>-2.500382420758064</v>
       </c>
       <c r="G48">
-        <v>-5.444272743092744</v>
+        <v>-4.917502047429451</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5809082286115407</v>
       </c>
       <c r="E49">
-        <v>-17.43377112465103</v>
+        <v>-17.98960960977451</v>
       </c>
       <c r="F49">
-        <v>-2.195985564720941</v>
+        <v>-2.246716441203188</v>
       </c>
       <c r="G49">
-        <v>-5.629464660559574</v>
+        <v>-5.448500309746393</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7539061276775796</v>
       </c>
       <c r="E50">
-        <v>-17.11035656797123</v>
+        <v>-17.44438586772501</v>
       </c>
       <c r="F50">
-        <v>-2.534251050388925</v>
+        <v>-2.645827997709004</v>
       </c>
       <c r="G50">
-        <v>-4.953944532725749</v>
+        <v>-5.113896851001176</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.961143902457993</v>
       </c>
       <c r="E51">
-        <v>-17.16067697114446</v>
+        <v>-16.38745361975677</v>
       </c>
       <c r="F51">
-        <v>-2.218676204618425</v>
+        <v>-2.595189070008468</v>
       </c>
       <c r="G51">
-        <v>-5.283453061886028</v>
+        <v>-5.810485290646922</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.199579516211487</v>
       </c>
       <c r="E52">
-        <v>-16.89465629403787</v>
+        <v>-15.88089398878476</v>
       </c>
       <c r="F52">
-        <v>-2.10554109821368</v>
+        <v>-2.692706965768234</v>
       </c>
       <c r="G52">
-        <v>-7.177532033996949</v>
+        <v>-6.101747087192002</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.465223728364076</v>
       </c>
       <c r="E53">
-        <v>-15.66689189260428</v>
+        <v>-15.65770814731672</v>
       </c>
       <c r="F53">
-        <v>-2.119135435661023</v>
+        <v>-2.619439525725423</v>
       </c>
       <c r="G53">
-        <v>-5.679616114933993</v>
+        <v>-6.905491264852878</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.749678645279889</v>
       </c>
       <c r="E54">
-        <v>-14.75996987461413</v>
+        <v>-15.18737177993206</v>
       </c>
       <c r="F54">
-        <v>-2.722569610639156</v>
+        <v>-2.882395645702696</v>
       </c>
       <c r="G54">
-        <v>-5.804228359577699</v>
+        <v>-5.922146681141</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.047168285968552</v>
       </c>
       <c r="E55">
-        <v>-13.5988419682034</v>
+        <v>-15.39983872342394</v>
       </c>
       <c r="F55">
-        <v>-1.76078783904697</v>
+        <v>-2.751531820143235</v>
       </c>
       <c r="G55">
-        <v>-6.506544043006386</v>
+        <v>-6.380951876883055</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.352918565280352</v>
       </c>
       <c r="E56">
-        <v>-14.4137499228317</v>
+        <v>-14.73165332664416</v>
       </c>
       <c r="F56">
-        <v>-1.984325267794625</v>
+        <v>-2.643358634481259</v>
       </c>
       <c r="G56">
-        <v>-6.591939565191886</v>
+        <v>-6.494208950327061</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.658868456521187</v>
       </c>
       <c r="E57">
-        <v>-13.33925172418771</v>
+        <v>-13.6420571956586</v>
       </c>
       <c r="F57">
-        <v>-2.951001862369953</v>
+        <v>-2.761417556728245</v>
       </c>
       <c r="G57">
-        <v>-6.39632273982189</v>
+        <v>-6.687375971997996</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.959141671280127</v>
       </c>
       <c r="E58">
-        <v>-13.56567089609722</v>
+        <v>-12.92461558709739</v>
       </c>
       <c r="F58">
-        <v>-2.224253602341474</v>
+        <v>-2.830894387535845</v>
       </c>
       <c r="G58">
-        <v>-7.583126831286297</v>
+        <v>-6.45574041116073</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.248881501077209</v>
       </c>
       <c r="E59">
-        <v>-12.8697123682284</v>
+        <v>-13.96522268626798</v>
       </c>
       <c r="F59">
-        <v>-2.706684837323073</v>
+        <v>-2.790714426663055</v>
       </c>
       <c r="G59">
-        <v>-6.697549278440176</v>
+        <v>-6.719266457177795</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.520221898807868</v>
       </c>
       <c r="E60">
-        <v>-11.86675047348357</v>
+        <v>-12.92905349162491</v>
       </c>
       <c r="F60">
-        <v>-2.076438894618528</v>
+        <v>-3.177409584168309</v>
       </c>
       <c r="G60">
-        <v>-6.955589750498668</v>
+        <v>-7.150107474749626</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.76809026213051</v>
       </c>
       <c r="E61">
-        <v>-14.46745762456267</v>
+        <v>-12.60428492121681</v>
       </c>
       <c r="F61">
-        <v>-2.274575265326739</v>
+        <v>-2.918398978130571</v>
       </c>
       <c r="G61">
-        <v>-6.838926125694752</v>
+        <v>-6.797156972625768</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.989713484763609</v>
       </c>
       <c r="E62">
-        <v>-10.29023017482325</v>
+        <v>-13.08788518896994</v>
       </c>
       <c r="F62">
-        <v>-2.382490000359041</v>
+        <v>-2.906117603016665</v>
       </c>
       <c r="G62">
-        <v>-7.846652877303362</v>
+        <v>-7.023121568954262</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.180887678761763</v>
       </c>
       <c r="E63">
-        <v>-13.05351859972573</v>
+        <v>-11.88095629644564</v>
       </c>
       <c r="F63">
-        <v>-3.062313732121137</v>
+        <v>-2.64234388441283</v>
       </c>
       <c r="G63">
-        <v>-8.785460691875425</v>
+        <v>-7.130495802974983</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.338971376402101</v>
       </c>
       <c r="E64">
-        <v>-11.68408541743618</v>
+        <v>-11.46629751698528</v>
       </c>
       <c r="F64">
-        <v>-2.54504384928</v>
+        <v>-2.532322611075208</v>
       </c>
       <c r="G64">
-        <v>-7.747578180949593</v>
+        <v>-7.726410552771493</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.464393055202845</v>
       </c>
       <c r="E65">
-        <v>-10.69627126824701</v>
+        <v>-11.38591710334914</v>
       </c>
       <c r="F65">
-        <v>-2.50360642668976</v>
+        <v>-2.75413123705322</v>
       </c>
       <c r="G65">
-        <v>-8.482261068115733</v>
+        <v>-8.137643209114222</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.558174342838419</v>
       </c>
       <c r="E66">
-        <v>-11.24070252734517</v>
+        <v>-11.43986481420251</v>
       </c>
       <c r="F66">
-        <v>-2.442987328520295</v>
+        <v>-3.055508693907139</v>
       </c>
       <c r="G66">
-        <v>-8.375161609374771</v>
+        <v>-7.697032771656001</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.620870755777376</v>
       </c>
       <c r="E67">
-        <v>-10.52889886892351</v>
+        <v>-11.48059843790151</v>
       </c>
       <c r="F67">
-        <v>-2.73784801901639</v>
+        <v>-3.071595588869505</v>
       </c>
       <c r="G67">
-        <v>-7.755278509873938</v>
+        <v>-7.55363649162247</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.65459255933648</v>
       </c>
       <c r="E68">
-        <v>-11.26022025031823</v>
+        <v>-11.75010151151999</v>
       </c>
       <c r="F68">
-        <v>-2.799029578652356</v>
+        <v>-2.751148286035739</v>
       </c>
       <c r="G68">
-        <v>-8.034231698104007</v>
+        <v>-7.333908963089963</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.662596788779974</v>
       </c>
       <c r="E69">
-        <v>-10.21845386180168</v>
+        <v>-10.8041893323238</v>
       </c>
       <c r="F69">
-        <v>-2.82223794817659</v>
+        <v>-2.85448214933056</v>
       </c>
       <c r="G69">
-        <v>-8.814242574793848</v>
+        <v>-7.457521422980809</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.646170280643664</v>
       </c>
       <c r="E70">
-        <v>-12.19982879369574</v>
+        <v>-10.67692562728624</v>
       </c>
       <c r="F70">
-        <v>-2.914507308072218</v>
+        <v>-3.360339614463329</v>
       </c>
       <c r="G70">
-        <v>-8.329721061302735</v>
+        <v>-6.712853930468227</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.607191756143914</v>
       </c>
       <c r="E71">
-        <v>-12.23149641243138</v>
+        <v>-10.81306061290483</v>
       </c>
       <c r="F71">
-        <v>-2.792414236573599</v>
+        <v>-2.955571965331198</v>
       </c>
       <c r="G71">
-        <v>-7.988009861284703</v>
+        <v>-7.668820302570332</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.549016078721125</v>
       </c>
       <c r="E72">
-        <v>-11.59797195570632</v>
+        <v>-10.80628601578935</v>
       </c>
       <c r="F72">
-        <v>-3.427983268208534</v>
+        <v>-3.000193632217799</v>
       </c>
       <c r="G72">
-        <v>-7.729972699771749</v>
+        <v>-8.360860052645121</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.471367827354541</v>
       </c>
       <c r="E73">
-        <v>-10.44850939833935</v>
+        <v>-12.17431989961054</v>
       </c>
       <c r="F73">
-        <v>-3.410175854150553</v>
+        <v>-3.506535692281205</v>
       </c>
       <c r="G73">
-        <v>-7.623952478876589</v>
+        <v>-7.5531332887005</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.373505918365623</v>
       </c>
       <c r="E74">
-        <v>-10.60305715927312</v>
+        <v>-11.25062441389598</v>
       </c>
       <c r="F74">
-        <v>-3.048067469527791</v>
+        <v>-3.343218916982269</v>
       </c>
       <c r="G74">
-        <v>-7.508460787193575</v>
+        <v>-7.811435293856595</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.257641543930769</v>
       </c>
       <c r="E75">
-        <v>-11.61583225719257</v>
+        <v>-11.98168767227225</v>
       </c>
       <c r="F75">
-        <v>-3.161775806175274</v>
+        <v>-3.172433581179692</v>
       </c>
       <c r="G75">
-        <v>-6.799050604674231</v>
+        <v>-7.822466031593447</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.122821781154728</v>
       </c>
       <c r="E76">
-        <v>-10.6385286961752</v>
+        <v>-12.9817105873861</v>
       </c>
       <c r="F76">
-        <v>-2.840002287129625</v>
+        <v>-2.778616120745168</v>
       </c>
       <c r="G76">
-        <v>-6.196047976878141</v>
+        <v>-7.331227421203153</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.968170351149252</v>
       </c>
       <c r="E77">
-        <v>-11.78297370434167</v>
+        <v>-12.8618599942991</v>
       </c>
       <c r="F77">
-        <v>-2.865015669224559</v>
+        <v>-3.063685508540173</v>
       </c>
       <c r="G77">
-        <v>-7.211372430499378</v>
+        <v>-6.520772767734173</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.796789095011849</v>
       </c>
       <c r="E78">
-        <v>-12.99650511196916</v>
+        <v>-13.81817407829091</v>
       </c>
       <c r="F78">
-        <v>-3.563328561417139</v>
+        <v>-3.151811374686998</v>
       </c>
       <c r="G78">
-        <v>-6.749425527040556</v>
+        <v>-6.712691713736803</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.609208034643803</v>
       </c>
       <c r="E79">
-        <v>-13.25301599365964</v>
+        <v>-14.19338532067044</v>
       </c>
       <c r="F79">
-        <v>-2.965349185786441</v>
+        <v>-3.285503246559616</v>
       </c>
       <c r="G79">
-        <v>-5.672207114017104</v>
+        <v>-6.969560252674393</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.40722243658232</v>
       </c>
       <c r="E80">
-        <v>-13.90042022321822</v>
+        <v>-14.93251379125438</v>
       </c>
       <c r="F80">
-        <v>-3.420344064019917</v>
+        <v>-3.132703423806622</v>
       </c>
       <c r="G80">
-        <v>-6.427286272250694</v>
+        <v>-6.571920696315913</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.19805221707322</v>
       </c>
       <c r="E81">
-        <v>-14.2118977224138</v>
+        <v>-15.18568718760121</v>
       </c>
       <c r="F81">
-        <v>-3.621526341668222</v>
+        <v>-3.485047841852586</v>
       </c>
       <c r="G81">
-        <v>-6.127238287844389</v>
+        <v>-6.49444068851481</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.986370623296622</v>
       </c>
       <c r="E82">
-        <v>-15.82045697467839</v>
+        <v>-15.02534297993762</v>
       </c>
       <c r="F82">
-        <v>-3.323306621353774</v>
+        <v>-3.365048054780841</v>
       </c>
       <c r="G82">
-        <v>-5.608525460023683</v>
+        <v>-6.820274512126498</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.776695420045839</v>
       </c>
       <c r="E83">
-        <v>-17.10897991187289</v>
+        <v>-17.00230717814821</v>
       </c>
       <c r="F83">
-        <v>-3.122250255550695</v>
+        <v>-3.497542935756414</v>
       </c>
       <c r="G83">
-        <v>-5.125046768377441</v>
+        <v>-6.416626315614241</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.57796683434047</v>
       </c>
       <c r="E84">
-        <v>-16.40378782550244</v>
+        <v>-17.60832115527668</v>
       </c>
       <c r="F84">
-        <v>-3.15662336092986</v>
+        <v>-3.477778917893021</v>
       </c>
       <c r="G84">
-        <v>-4.831894650329438</v>
+        <v>-5.504806068278318</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.396500653226909</v>
       </c>
       <c r="E85">
-        <v>-18.52278761096361</v>
+        <v>-18.52521487303172</v>
       </c>
       <c r="F85">
-        <v>-3.450419599313359</v>
+        <v>-3.391747992907875</v>
       </c>
       <c r="G85">
-        <v>-5.709692421158271</v>
+        <v>-5.330247623083626</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.23868838493154</v>
       </c>
       <c r="E86">
-        <v>-19.27524338055213</v>
+        <v>-19.25261006746179</v>
       </c>
       <c r="F86">
-        <v>-3.065966832367483</v>
+        <v>-3.430658066552173</v>
       </c>
       <c r="G86">
-        <v>-6.118111113792619</v>
+        <v>-5.086555055392335</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.113253370282681</v>
       </c>
       <c r="E87">
-        <v>-21.13823041646366</v>
+        <v>-20.40247565901544</v>
       </c>
       <c r="F87">
-        <v>-3.317250427271907</v>
+        <v>-3.459316265219425</v>
       </c>
       <c r="G87">
-        <v>-4.683234602888465</v>
+        <v>-5.611147412090786</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.025541057820093</v>
       </c>
       <c r="E88">
-        <v>-21.75778453087507</v>
+        <v>-21.95175265804561</v>
       </c>
       <c r="F88">
-        <v>-3.197955580859945</v>
+        <v>-3.139317109150573</v>
       </c>
       <c r="G88">
-        <v>-5.583620225931746</v>
+        <v>-5.276517468981255</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.982415159516222</v>
       </c>
       <c r="E89">
-        <v>-23.5703470087112</v>
+        <v>-24.03761307071866</v>
       </c>
       <c r="F89">
-        <v>-3.998908164463801</v>
+        <v>-3.786669667090331</v>
       </c>
       <c r="G89">
-        <v>-4.34726057828999</v>
+        <v>-5.167163528728048</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.991330626894357</v>
       </c>
       <c r="E90">
-        <v>-24.32976757132351</v>
+        <v>-24.44411154001719</v>
       </c>
       <c r="F90">
-        <v>-3.156881811559534</v>
+        <v>-3.367853735174124</v>
       </c>
       <c r="G90">
-        <v>-5.263566614831626</v>
+        <v>-5.690676647580698</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.05414254151101</v>
       </c>
       <c r="E91">
-        <v>-26.74074071842923</v>
+        <v>-26.89985770963674</v>
       </c>
       <c r="F91">
-        <v>-4.235059972021286</v>
+        <v>-3.554301841828833</v>
       </c>
       <c r="G91">
-        <v>-4.666503105732988</v>
+        <v>-5.294367930529005</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.173243573185835</v>
       </c>
       <c r="E92">
-        <v>-27.93695071297738</v>
+        <v>-28.23559904530923</v>
       </c>
       <c r="F92">
-        <v>-3.285644069018092</v>
+        <v>-3.642381319401102</v>
       </c>
       <c r="G92">
-        <v>-5.097718214950757</v>
+        <v>-5.871660861667115</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.347926422158703</v>
       </c>
       <c r="E93">
-        <v>-28.92030431526899</v>
+        <v>-29.209601348775</v>
       </c>
       <c r="F93">
-        <v>-3.371351102348743</v>
+        <v>-3.472667891017748</v>
       </c>
       <c r="G93">
-        <v>-5.686826483118526</v>
+        <v>-5.726847668142775</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.570173710042667</v>
       </c>
       <c r="E94">
-        <v>-32.04229995903005</v>
+        <v>-32.07942891741894</v>
       </c>
       <c r="F94">
-        <v>-3.937866598918908</v>
+        <v>-3.557211068147465</v>
       </c>
       <c r="G94">
-        <v>-5.623595063318445</v>
+        <v>-6.005218200357932</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.833011110366789</v>
       </c>
       <c r="E95">
-        <v>-31.60138735151023</v>
+        <v>-32.92492444973204</v>
       </c>
       <c r="F95">
-        <v>-3.69486999151209</v>
+        <v>-3.628514449078238</v>
       </c>
       <c r="G95">
-        <v>-5.073461847784517</v>
+        <v>-6.567305795834169</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.127770653329279</v>
       </c>
       <c r="E96">
-        <v>-35.0500535247626</v>
+        <v>-35.62870872617373</v>
       </c>
       <c r="F96">
-        <v>-4.02668083837746</v>
+        <v>-3.89018328611156</v>
       </c>
       <c r="G96">
-        <v>-5.848116261791818</v>
+        <v>-5.867992777209602</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.435402055987259</v>
       </c>
       <c r="E97">
-        <v>-36.59232723873991</v>
+        <v>-38.75522605123144</v>
       </c>
       <c r="F97">
-        <v>-4.148834380696483</v>
+        <v>-3.782695160291699</v>
       </c>
       <c r="G97">
-        <v>-6.313370400244373</v>
+        <v>-6.795779785681431</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.746991729754525</v>
       </c>
       <c r="E98">
-        <v>-39.31074754317439</v>
+        <v>-39.94316478800458</v>
       </c>
       <c r="F98">
-        <v>-4.048182771051927</v>
+        <v>-3.705705037140707</v>
       </c>
       <c r="G98">
-        <v>-6.261341866549187</v>
+        <v>-6.739623001698773</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.042626852596258</v>
       </c>
       <c r="E99">
-        <v>-42.0405207319461</v>
+        <v>-41.91089769195054</v>
       </c>
       <c r="F99">
-        <v>-4.70399958711349</v>
+        <v>-4.011038776710397</v>
       </c>
       <c r="G99">
-        <v>-6.164971885901003</v>
+        <v>-6.502193986167783</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.319557571901717</v>
       </c>
       <c r="E100">
-        <v>-44.51427890693116</v>
+        <v>-44.77072186151153</v>
       </c>
       <c r="F100">
-        <v>-4.221465634573944</v>
+        <v>-4.342111548219872</v>
       </c>
       <c r="G100">
-        <v>-6.208823372114188</v>
+        <v>-7.432497009249458</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.552753830348474</v>
       </c>
       <c r="E101">
-        <v>-46.31033736124633</v>
+        <v>-47.10030248104039</v>
       </c>
       <c r="F101">
-        <v>-4.953043276560744</v>
+        <v>-4.520454079838189</v>
       </c>
       <c r="G101">
-        <v>-6.908997132578966</v>
+        <v>-7.20695616274999</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.767958253698102</v>
       </c>
       <c r="E102">
-        <v>-48.32008997550947</v>
+        <v>-48.65277205424596</v>
       </c>
       <c r="F102">
-        <v>-4.83159964510592</v>
+        <v>-4.281362396368168</v>
       </c>
       <c r="G102">
-        <v>-7.514270794614996</v>
+        <v>-7.469303654555075</v>
       </c>
     </row>
   </sheetData>
